--- a/final_capital.xlsx
+++ b/final_capital.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,6 +441,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Transaction Count</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Final Capital (%)</t>
         </is>
       </c>
@@ -454,7 +459,10 @@
       <c r="B2" t="n">
         <v>851759.2463262253</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" t="inlineStr">
         <is>
           <t>-14.82%</t>
         </is>
@@ -469,7 +477,10 @@
       <c r="B3" t="n">
         <v>884909.2970161092</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>-11.51%</t>
         </is>
@@ -484,7 +495,10 @@
       <c r="B4" t="n">
         <v>889739.1628526091</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="n">
+        <v>44</v>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>-11.03%</t>
         </is>
@@ -499,7 +513,10 @@
       <c r="B5" t="n">
         <v>902799.3520907948</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="n">
+        <v>58</v>
+      </c>
+      <c r="D5" t="inlineStr">
         <is>
           <t>-9.72%</t>
         </is>
@@ -514,7 +531,10 @@
       <c r="B6" t="n">
         <v>867698.667432182</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="n">
+        <v>69</v>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>-13.23%</t>
         </is>
@@ -529,7 +549,10 @@
       <c r="B7" t="n">
         <v>900570.7608164254</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="n">
+        <v>77</v>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>-9.94%</t>
         </is>
@@ -544,7 +567,10 @@
       <c r="B8" t="n">
         <v>905119.0535460737</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="n">
+        <v>85</v>
+      </c>
+      <c r="D8" t="inlineStr">
         <is>
           <t>-9.49%</t>
         </is>
@@ -559,7 +585,10 @@
       <c r="B9" t="n">
         <v>870968.2718870143</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="n">
+        <v>90</v>
+      </c>
+      <c r="D9" t="inlineStr">
         <is>
           <t>-12.9%</t>
         </is>
@@ -574,7 +603,10 @@
       <c r="B10" t="n">
         <v>742286.5371046157</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="n">
+        <v>106</v>
+      </c>
+      <c r="D10" t="inlineStr">
         <is>
           <t>-25.77%</t>
         </is>
@@ -589,7 +621,10 @@
       <c r="B11" t="n">
         <v>742579.94355152</v>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" t="n">
+        <v>110</v>
+      </c>
+      <c r="D11" t="inlineStr">
         <is>
           <t>-25.74%</t>
         </is>
@@ -604,7 +639,10 @@
       <c r="B12" t="n">
         <v>793506.3984187843</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" t="n">
+        <v>116</v>
+      </c>
+      <c r="D12" t="inlineStr">
         <is>
           <t>-20.65%</t>
         </is>
@@ -619,7 +657,10 @@
       <c r="B13" t="n">
         <v>793506.3984187843</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" t="n">
+        <v>116</v>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>-20.65%</t>
         </is>
@@ -634,7 +675,10 @@
       <c r="B14" t="n">
         <v>1038919.507868996</v>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" t="n">
+        <v>21</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>3.89%</t>
         </is>
@@ -649,7 +693,10 @@
       <c r="B15" t="n">
         <v>1044589.966813037</v>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>4.46%</t>
         </is>
@@ -664,7 +711,10 @@
       <c r="B16" t="n">
         <v>1059923.160194285</v>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" t="n">
+        <v>44</v>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>5.99%</t>
         </is>
@@ -679,7 +729,10 @@
       <c r="B17" t="n">
         <v>1018713.528705096</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" t="n">
+        <v>55</v>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>1.87%</t>
         </is>
@@ -694,7 +747,10 @@
       <c r="B18" t="n">
         <v>1057306.703391518</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" t="n">
+        <v>63</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>5.73%</t>
         </is>
@@ -709,7 +765,10 @@
       <c r="B19" t="n">
         <v>1062646.584055293</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" t="n">
+        <v>71</v>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t>6.26%</t>
         </is>
@@ -724,7 +783,10 @@
       <c r="B20" t="n">
         <v>1022552.177324332</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" t="n">
+        <v>76</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>2.26%</t>
         </is>
@@ -739,7 +801,10 @@
       <c r="B21" t="n">
         <v>871474.5866349166</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" t="n">
+        <v>92</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>-12.85%</t>
         </is>
@@ -754,7 +819,10 @@
       <c r="B22" t="n">
         <v>871819.05773772</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" t="n">
+        <v>96</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>-12.82%</t>
         </is>
@@ -769,7 +837,10 @@
       <c r="B23" t="n">
         <v>931608.787155884</v>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" t="n">
+        <v>102</v>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>-6.84%</t>
         </is>
@@ -784,7 +855,10 @@
       <c r="B24" t="n">
         <v>931608.787155884</v>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" t="n">
+        <v>102</v>
+      </c>
+      <c r="D24" t="inlineStr">
         <is>
           <t>-6.84%</t>
         </is>
@@ -799,7 +873,10 @@
       <c r="B25" t="n">
         <v>1005458.034911359</v>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" t="n">
+        <v>9</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>0.55%</t>
         </is>
@@ -814,7 +891,10 @@
       <c r="B26" t="n">
         <v>1020216.823503844</v>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" t="n">
+        <v>23</v>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>2.02%</t>
         </is>
@@ -829,7 +909,10 @@
       <c r="B27" t="n">
         <v>980550.9676054247</v>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" t="n">
+        <v>34</v>
+      </c>
+      <c r="D27" t="inlineStr">
         <is>
           <t>-1.94%</t>
         </is>
@@ -844,7 +927,10 @@
       <c r="B28" t="n">
         <v>1017698.383159863</v>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" t="n">
+        <v>42</v>
+      </c>
+      <c r="D28" t="inlineStr">
         <is>
           <t>1.77%</t>
         </is>
@@ -859,7 +945,10 @@
       <c r="B29" t="n">
         <v>1022838.223757069</v>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" t="n">
+        <v>50</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>2.28%</t>
         </is>
@@ -874,7 +963,10 @@
       <c r="B30" t="n">
         <v>984245.8145980573</v>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" t="n">
+        <v>55</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>-1.58%</t>
         </is>
@@ -889,7 +981,10 @@
       <c r="B31" t="n">
         <v>838827.820667707</v>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" t="n">
+        <v>71</v>
+      </c>
+      <c r="D31" t="inlineStr">
         <is>
           <t>-16.12%</t>
         </is>
@@ -904,7 +999,10 @@
       <c r="B32" t="n">
         <v>839159.387358094</v>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" t="n">
+        <v>75</v>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>-16.08%</t>
         </is>
@@ -919,7 +1017,10 @@
       <c r="B33" t="n">
         <v>896709.3024047408</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" t="n">
+        <v>81</v>
+      </c>
+      <c r="D33" t="inlineStr">
         <is>
           <t>-10.33%</t>
         </is>
@@ -934,7 +1035,10 @@
       <c r="B34" t="n">
         <v>896709.3024047408</v>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" t="n">
+        <v>81</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>-10.33%</t>
         </is>
@@ -949,7 +1053,10 @@
       <c r="B35" t="n">
         <v>1014678.671888863</v>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" t="n">
+        <v>14</v>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t>1.47%</t>
         </is>
@@ -964,7 +1071,10 @@
       <c r="B36" t="n">
         <v>975228.1383796093</v>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" t="n">
+        <v>25</v>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t>-2.48%</t>
         </is>
@@ -979,7 +1089,10 @@
       <c r="B37" t="n">
         <v>1012173.902662763</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" t="n">
+        <v>33</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>1.22%</t>
         </is>
@@ -994,7 +1107,10 @@
       <c r="B38" t="n">
         <v>1017285.842115969</v>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" t="n">
+        <v>41</v>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t>1.73%</t>
         </is>
@@ -1009,7 +1125,10 @@
       <c r="B39" t="n">
         <v>978902.9282408865</v>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" t="n">
+        <v>46</v>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t>-2.11%</t>
         </is>
@@ -1024,7 +1143,10 @@
       <c r="B40" t="n">
         <v>834274.3222909927</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" t="n">
+        <v>62</v>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>-16.57%</t>
         </is>
@@ -1039,7 +1161,10 @@
       <c r="B41" t="n">
         <v>834604.0891026097</v>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" t="n">
+        <v>66</v>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>-16.54%</t>
         </is>
@@ -1054,7 +1179,10 @@
       <c r="B42" t="n">
         <v>891841.5998175347</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" t="n">
+        <v>72</v>
+      </c>
+      <c r="D42" t="inlineStr">
         <is>
           <t>-10.82%</t>
         </is>
@@ -1069,7 +1197,10 @@
       <c r="B43" t="n">
         <v>891841.5998175347</v>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" t="n">
+        <v>72</v>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>-10.82%</t>
         </is>
@@ -1084,7 +1215,10 @@
       <c r="B44" t="n">
         <v>961120.1707474395</v>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" t="n">
+        <v>11</v>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>-3.89%</t>
         </is>
@@ -1099,7 +1233,10 @@
       <c r="B45" t="n">
         <v>997531.4655806876</v>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" t="n">
+        <v>19</v>
+      </c>
+      <c r="D45" t="inlineStr">
         <is>
           <t>-0.25%</t>
         </is>
@@ -1114,7 +1251,10 @@
       <c r="B46" t="n">
         <v>1002569.454054112</v>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" t="n">
+        <v>27</v>
+      </c>
+      <c r="D46" t="inlineStr">
         <is>
           <t>0.26%</t>
         </is>
@@ -1129,7 +1269,10 @@
       <c r="B47" t="n">
         <v>964741.7999026448</v>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" t="n">
+        <v>32</v>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>-3.53%</t>
         </is>
@@ -1144,7 +1287,10 @@
       <c r="B48" t="n">
         <v>822205.4384349667</v>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" t="n">
+        <v>48</v>
+      </c>
+      <c r="D48" t="inlineStr">
         <is>
           <t>-17.78%</t>
         </is>
@@ -1159,7 +1305,10 @@
       <c r="B49" t="n">
         <v>822530.434732566</v>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" t="n">
+        <v>52</v>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>-17.75%</t>
         </is>
@@ -1174,7 +1323,10 @@
       <c r="B50" t="n">
         <v>878939.9289898711</v>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" t="n">
+        <v>58</v>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>-12.11%</t>
         </is>
@@ -1189,7 +1341,10 @@
       <c r="B51" t="n">
         <v>878939.9289898711</v>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" t="n">
+        <v>58</v>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>-12.11%</t>
         </is>
@@ -1204,7 +1359,10 @@
       <c r="B52" t="n">
         <v>1037884.227114838</v>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D52" t="inlineStr">
         <is>
           <t>3.79%</t>
         </is>
@@ -1219,7 +1377,10 @@
       <c r="B53" t="n">
         <v>1043126.015422648</v>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" t="n">
+        <v>16</v>
+      </c>
+      <c r="D53" t="inlineStr">
         <is>
           <t>4.31%</t>
         </is>
@@ -1234,7 +1395,10 @@
       <c r="B54" t="n">
         <v>1003768.133543996</v>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" t="n">
+        <v>21</v>
+      </c>
+      <c r="D54" t="inlineStr">
         <is>
           <t>0.38%</t>
         </is>
@@ -1249,7 +1413,10 @@
       <c r="B55" t="n">
         <v>855465.8027783954</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" t="n">
+        <v>37</v>
+      </c>
+      <c r="D55" t="inlineStr">
         <is>
           <t>-14.45%</t>
         </is>
@@ -1264,7 +1431,10 @@
       <c r="B56" t="n">
         <v>855803.9460277942</v>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" t="n">
+        <v>41</v>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>-14.42%</t>
         </is>
@@ -1279,7 +1449,10 @@
       <c r="B57" t="n">
         <v>914495.3521330653</v>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" t="n">
+        <v>47</v>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>-8.55%</t>
         </is>
@@ -1294,7 +1467,10 @@
       <c r="B58" t="n">
         <v>914495.3521330653</v>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" t="n">
+        <v>47</v>
+      </c>
+      <c r="D58" t="inlineStr">
         <is>
           <t>-8.55%</t>
         </is>
@@ -1309,7 +1485,10 @@
       <c r="B59" t="n">
         <v>1005050.455697146</v>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" t="n">
+        <v>8</v>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>0.51%</t>
         </is>
@@ -1324,7 +1503,10 @@
       <c r="B60" t="n">
         <v>967129.191600031</v>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" t="n">
+        <v>13</v>
+      </c>
+      <c r="D60" t="inlineStr">
         <is>
           <t>-3.29%</t>
         </is>
@@ -1339,7 +1521,10 @@
       <c r="B61" t="n">
         <v>824240.1035002344</v>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" t="n">
+        <v>29</v>
+      </c>
+      <c r="D61" t="inlineStr">
         <is>
           <t>-17.58%</t>
         </is>
@@ -1354,7 +1539,10 @@
       <c r="B62" t="n">
         <v>824565.9040476991</v>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" t="n">
+        <v>33</v>
+      </c>
+      <c r="D62" t="inlineStr">
         <is>
           <t>-17.54%</t>
         </is>
@@ -1369,7 +1557,10 @@
       <c r="B63" t="n">
         <v>881114.9916741913</v>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" t="n">
+        <v>39</v>
+      </c>
+      <c r="D63" t="inlineStr">
         <is>
           <t>-11.89%</t>
         </is>
@@ -1384,7 +1575,10 @@
       <c r="B64" t="n">
         <v>881114.9916741913</v>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" t="n">
+        <v>39</v>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>-11.89%</t>
         </is>
@@ -1399,7 +1593,10 @@
       <c r="B65" t="n">
         <v>962269.2931661713</v>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" t="inlineStr">
         <is>
           <t>-3.77%</t>
         </is>
@@ -1414,7 +1611,10 @@
       <c r="B66" t="n">
         <v>820098.2337036069</v>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" t="n">
+        <v>21</v>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>-17.99%</t>
         </is>
@@ -1429,7 +1629,10 @@
       <c r="B67" t="n">
         <v>820422.3970783087</v>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" t="n">
+        <v>25</v>
+      </c>
+      <c r="D67" t="inlineStr">
         <is>
           <t>-17.96%</t>
         </is>
@@ -1444,7 +1647,10 @@
       <c r="B68" t="n">
         <v>876687.3211982299</v>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" t="n">
+        <v>31</v>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>-12.33%</t>
         </is>
@@ -1459,7 +1665,10 @@
       <c r="B69" t="n">
         <v>876687.3211982299</v>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" t="n">
+        <v>31</v>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>-12.33%</t>
         </is>
@@ -1474,7 +1683,10 @@
       <c r="B70" t="n">
         <v>852254.3944068127</v>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" t="n">
+        <v>16</v>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>-14.77%</t>
         </is>
@@ -1489,7 +1701,10 @@
       <c r="B71" t="n">
         <v>852591.2682705055</v>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" t="n">
+        <v>20</v>
+      </c>
+      <c r="D71" t="inlineStr">
         <is>
           <t>-14.74%</t>
         </is>
@@ -1504,7 +1719,10 @@
       <c r="B72" t="n">
         <v>911062.3475406249</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" t="n">
+        <v>26</v>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>-8.89%</t>
         </is>
@@ -1519,7 +1737,10 @@
       <c r="B73" t="n">
         <v>911062.3475406249</v>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" t="n">
+        <v>26</v>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>-8.89%</t>
         </is>
@@ -1534,7 +1755,10 @@
       <c r="B74" t="n">
         <v>1000395.273835962</v>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" t="n">
+        <v>4</v>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>0.04%</t>
         </is>
@@ -1549,7 +1773,10 @@
       <c r="B75" t="n">
         <v>1069002.815966404</v>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" t="n">
+        <v>10</v>
+      </c>
+      <c r="D75" t="inlineStr">
         <is>
           <t>6.9%</t>
         </is>
@@ -1564,7 +1791,10 @@
       <c r="B76" t="n">
         <v>1069002.815966404</v>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" t="n">
+        <v>10</v>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>6.9%</t>
         </is>
@@ -1579,7 +1809,10 @@
       <c r="B77" t="n">
         <v>1068580.434079191</v>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" t="n">
+        <v>6</v>
+      </c>
+      <c r="D77" t="inlineStr">
         <is>
           <t>6.86%</t>
         </is>
@@ -1594,7 +1827,10 @@
       <c r="B78" t="n">
         <v>1068580.434079191</v>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" t="n">
+        <v>6</v>
+      </c>
+      <c r="D78" t="inlineStr">
         <is>
           <t>6.86%</t>
         </is>
@@ -1609,7 +1845,10 @@
       <c r="B79" t="n">
         <v>1000000</v>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
